--- a/docs/collections/honzosho/metadata/data.xlsx
+++ b/docs/collections/honzosho/metadata/data.xlsx
@@ -17024,7 +17024,7 @@
     <t>https://kotenseki.nijl.ac.jp/biblio/100303829/manifest</t>
   </si>
   <si>
-    <t>子書誌1:1 藥性歌括 やくしょううたくくり Yakushouutakukuri 内・外 ; 1 尾張醫學館 [編] ; 100304261 ; DIGTOKY006750001 1  42  1 Y|子書誌2:1 諸病主藥 しょびょうしゅやく Shobyoushuyaku 内 ; 100304263 ; DIGTOKY00675000201 1  15  43 Y|子書誌2ー1:1 十四經穴分寸歌 じゅうしけいけつぶんすんのうた Juushikeiketsubunsunnouta 内 ; 100304264 ; DIGTOKY00675000202 1  21  57 Y|子書誌2-2:1 五藏六府變化傍通訣 ごぞうろっぷへんかぼうつうけつ Gozouroppuhenkaboutsuuketsu 内 ; 100304265 ; DIGTOKY00675000203 1  12  78 Y</t>
+    <t>子書誌1:1 藥性歌括 やくしょううたくくり Yakushouutakukuri 内・外 ; 1 尾張醫學館 [編] ; 100304261 ; DIGTOKY006750001 1  42  1 Y|子書誌2:1 諸病主藥/十四經穴分寸歌 しょびょうしゅやく/じゅうしけいけつぶんすんのうた Shobyoushuyaku Juushikeiketsubunsunnouta 外 ; 1 尾張醫學館 [編] ; 100304267 ; DIGTOKY0067400020E 1  47  43 Y|子書誌2ー1:1 諸病主藥 しょびょうしゅやく Shobyoushuyaku 内 ; 100304263 ; DIGTOKY00675000201 1  15  43 Y|子書誌2ー2:1 十四經穴分寸歌 じゅうしけいけつぶんすんのうた Juushikeiketsubunsunnouta 内 ; 100304264 ; DIGTOKY00675000202 1  21  57 Y|子書誌2-3:1 五藏六府變化傍通訣 ごぞうろっぷへんかぼうつうけつ Gozouroppuhenkaboutsuuketsu 内 ; 100304265 ; DIGTOKY00675000203 1  12  78 Y</t>
   </si>
   <si>
     <t>E3:369</t>

--- a/docs/collections/honzosho/metadata/data.xlsx
+++ b/docs/collections/honzosho/metadata/data.xlsx
@@ -43785,7 +43785,7 @@
       <c r="AF379" t="inlineStr"/>
       <c r="AG379" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303664/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303664/manifest</t>
         </is>
       </c>
       <c r="AH379" t="inlineStr"/>
@@ -43919,7 +43919,7 @@
       <c r="AF380" t="inlineStr"/>
       <c r="AG380" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303665/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303665/manifest</t>
         </is>
       </c>
       <c r="AH380" t="inlineStr"/>
@@ -44053,7 +44053,7 @@
       <c r="AF381" t="inlineStr"/>
       <c r="AG381" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303666/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303666/manifest</t>
         </is>
       </c>
       <c r="AH381" t="inlineStr"/>
@@ -44187,7 +44187,7 @@
       <c r="AF382" t="inlineStr"/>
       <c r="AG382" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303667/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303667/manifest</t>
         </is>
       </c>
       <c r="AH382" t="inlineStr"/>
@@ -44321,7 +44321,7 @@
       <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303668/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303668/manifest</t>
         </is>
       </c>
       <c r="AH383" t="inlineStr"/>
@@ -44451,7 +44451,7 @@
       <c r="AF384" t="inlineStr"/>
       <c r="AG384" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303669/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303669/manifest</t>
         </is>
       </c>
       <c r="AH384" t="inlineStr"/>
@@ -44581,7 +44581,7 @@
       <c r="AF385" t="inlineStr"/>
       <c r="AG385" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303670/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303670/manifest</t>
         </is>
       </c>
       <c r="AH385" t="inlineStr"/>
@@ -44715,7 +44715,7 @@
       <c r="AF386" t="inlineStr"/>
       <c r="AG386" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303671/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303671/manifest</t>
         </is>
       </c>
       <c r="AH386" t="inlineStr"/>
@@ -44849,7 +44849,7 @@
       <c r="AF387" t="inlineStr"/>
       <c r="AG387" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303672/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303672/manifest</t>
         </is>
       </c>
       <c r="AH387" t="inlineStr"/>
@@ -44979,7 +44979,7 @@
       <c r="AF388" t="inlineStr"/>
       <c r="AG388" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303673/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303673/manifest</t>
         </is>
       </c>
       <c r="AH388" t="inlineStr"/>
@@ -45113,7 +45113,7 @@
       <c r="AF389" t="inlineStr"/>
       <c r="AG389" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303674/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303674/manifest</t>
         </is>
       </c>
       <c r="AH389" t="inlineStr"/>
@@ -45247,7 +45247,7 @@
       <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303675/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303675/manifest</t>
         </is>
       </c>
       <c r="AH390" t="inlineStr"/>
@@ -45381,7 +45381,7 @@
       <c r="AF391" t="inlineStr"/>
       <c r="AG391" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303676/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303676/manifest</t>
         </is>
       </c>
       <c r="AH391" t="inlineStr"/>
@@ -45511,7 +45511,7 @@
       <c r="AF392" t="inlineStr"/>
       <c r="AG392" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303677/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303677/manifest</t>
         </is>
       </c>
       <c r="AH392" t="inlineStr"/>
@@ -45645,7 +45645,7 @@
       <c r="AF393" t="inlineStr"/>
       <c r="AG393" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303678/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303678/manifest</t>
         </is>
       </c>
       <c r="AH393" t="inlineStr"/>
@@ -45779,7 +45779,7 @@
       <c r="AF394" t="inlineStr"/>
       <c r="AG394" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303679/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303679/manifest</t>
         </is>
       </c>
       <c r="AH394" t="inlineStr"/>
@@ -45909,7 +45909,7 @@
       <c r="AF395" t="inlineStr"/>
       <c r="AG395" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303680/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303680/manifest</t>
         </is>
       </c>
       <c r="AH395" t="inlineStr"/>
@@ -46043,7 +46043,7 @@
       <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303681/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303681/manifest</t>
         </is>
       </c>
       <c r="AH396" t="inlineStr"/>
@@ -46177,7 +46177,7 @@
       <c r="AF397" t="inlineStr"/>
       <c r="AG397" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303682/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303682/manifest</t>
         </is>
       </c>
       <c r="AH397" t="inlineStr"/>
@@ -46311,7 +46311,7 @@
       <c r="AF398" t="inlineStr"/>
       <c r="AG398" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303683/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303683/manifest</t>
         </is>
       </c>
       <c r="AH398" t="inlineStr"/>
@@ -46445,7 +46445,7 @@
       <c r="AF399" t="inlineStr"/>
       <c r="AG399" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303684/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303684/manifest</t>
         </is>
       </c>
       <c r="AH399" t="inlineStr"/>
@@ -46579,7 +46579,7 @@
       <c r="AF400" t="inlineStr"/>
       <c r="AG400" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303685/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303685/manifest</t>
         </is>
       </c>
       <c r="AH400" t="inlineStr"/>
@@ -46713,7 +46713,7 @@
       <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303686/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303686/manifest</t>
         </is>
       </c>
       <c r="AH401" t="inlineStr"/>
@@ -46847,7 +46847,7 @@
       <c r="AF402" t="inlineStr"/>
       <c r="AG402" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303687/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303687/manifest</t>
         </is>
       </c>
       <c r="AH402" t="inlineStr"/>
@@ -46981,7 +46981,7 @@
       <c r="AF403" t="inlineStr"/>
       <c r="AG403" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303688/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303688/manifest</t>
         </is>
       </c>
       <c r="AH403" t="inlineStr"/>
@@ -47115,7 +47115,7 @@
       <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303689/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303689/manifest</t>
         </is>
       </c>
       <c r="AH404" t="inlineStr"/>
@@ -47249,7 +47249,7 @@
       <c r="AF405" t="inlineStr"/>
       <c r="AG405" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303690/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303690/manifest</t>
         </is>
       </c>
       <c r="AH405" t="inlineStr"/>
@@ -47383,7 +47383,7 @@
       <c r="AF406" t="inlineStr"/>
       <c r="AG406" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303691/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303691/manifest</t>
         </is>
       </c>
       <c r="AH406" t="inlineStr"/>
@@ -47517,7 +47517,7 @@
       <c r="AF407" t="inlineStr"/>
       <c r="AG407" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303692/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303692/manifest</t>
         </is>
       </c>
       <c r="AH407" t="inlineStr"/>
@@ -47651,7 +47651,7 @@
       <c r="AF408" t="inlineStr"/>
       <c r="AG408" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303693/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303693/manifest</t>
         </is>
       </c>
       <c r="AH408" t="inlineStr"/>
@@ -47785,7 +47785,7 @@
       <c r="AF409" t="inlineStr"/>
       <c r="AG409" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303694/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303694/manifest</t>
         </is>
       </c>
       <c r="AH409" t="inlineStr"/>
@@ -47919,7 +47919,7 @@
       <c r="AF410" t="inlineStr"/>
       <c r="AG410" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303695/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303695/manifest</t>
         </is>
       </c>
       <c r="AH410" t="inlineStr"/>
@@ -48053,7 +48053,7 @@
       <c r="AF411" t="inlineStr"/>
       <c r="AG411" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303696/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303696/manifest</t>
         </is>
       </c>
       <c r="AH411" t="inlineStr"/>
@@ -48187,7 +48187,7 @@
       <c r="AF412" t="inlineStr"/>
       <c r="AG412" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303697/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303697/manifest</t>
         </is>
       </c>
       <c r="AH412" t="inlineStr"/>
@@ -48321,7 +48321,7 @@
       <c r="AF413" t="inlineStr"/>
       <c r="AG413" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303698/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303698/manifest</t>
         </is>
       </c>
       <c r="AH413" t="inlineStr"/>
@@ -48455,7 +48455,7 @@
       <c r="AF414" t="inlineStr"/>
       <c r="AG414" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303699/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303699/manifest</t>
         </is>
       </c>
       <c r="AH414" t="inlineStr"/>
@@ -48589,7 +48589,7 @@
       <c r="AF415" t="inlineStr"/>
       <c r="AG415" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303700/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303700/manifest</t>
         </is>
       </c>
       <c r="AH415" t="inlineStr"/>
@@ -48723,7 +48723,7 @@
       <c r="AF416" t="inlineStr"/>
       <c r="AG416" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303701/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303701/manifest</t>
         </is>
       </c>
       <c r="AH416" t="inlineStr"/>
@@ -48857,7 +48857,7 @@
       <c r="AF417" t="inlineStr"/>
       <c r="AG417" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303702/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303702/manifest</t>
         </is>
       </c>
       <c r="AH417" t="inlineStr"/>
@@ -48991,7 +48991,7 @@
       <c r="AF418" t="inlineStr"/>
       <c r="AG418" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303703/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303703/manifest</t>
         </is>
       </c>
       <c r="AH418" t="inlineStr"/>
@@ -49125,7 +49125,7 @@
       <c r="AF419" t="inlineStr"/>
       <c r="AG419" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303704/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303704/manifest</t>
         </is>
       </c>
       <c r="AH419" t="inlineStr"/>
@@ -49259,7 +49259,7 @@
       <c r="AF420" t="inlineStr"/>
       <c r="AG420" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303705/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303705/manifest</t>
         </is>
       </c>
       <c r="AH420" t="inlineStr"/>
@@ -49393,7 +49393,7 @@
       <c r="AF421" t="inlineStr"/>
       <c r="AG421" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303706/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303706/manifest</t>
         </is>
       </c>
       <c r="AH421" t="inlineStr"/>
@@ -49527,7 +49527,7 @@
       <c r="AF422" t="inlineStr"/>
       <c r="AG422" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303707/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303707/manifest</t>
         </is>
       </c>
       <c r="AH422" t="inlineStr"/>
@@ -49661,7 +49661,7 @@
       <c r="AF423" t="inlineStr"/>
       <c r="AG423" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303708/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303708/manifest</t>
         </is>
       </c>
       <c r="AH423" t="inlineStr"/>
@@ -49795,7 +49795,7 @@
       <c r="AF424" t="inlineStr"/>
       <c r="AG424" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303709/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303709/manifest</t>
         </is>
       </c>
       <c r="AH424" t="inlineStr"/>
@@ -49929,7 +49929,7 @@
       <c r="AF425" t="inlineStr"/>
       <c r="AG425" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303710/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303710/manifest</t>
         </is>
       </c>
       <c r="AH425" t="inlineStr"/>
@@ -50063,7 +50063,7 @@
       <c r="AF426" t="inlineStr"/>
       <c r="AG426" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303711/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303711/manifest</t>
         </is>
       </c>
       <c r="AH426" t="inlineStr"/>
@@ -50197,7 +50197,7 @@
       <c r="AF427" t="inlineStr"/>
       <c r="AG427" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303712/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303712/manifest</t>
         </is>
       </c>
       <c r="AH427" t="inlineStr"/>
@@ -50331,7 +50331,7 @@
       <c r="AF428" t="inlineStr"/>
       <c r="AG428" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303713/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303713/manifest</t>
         </is>
       </c>
       <c r="AH428" t="inlineStr"/>
@@ -50461,7 +50461,7 @@
       <c r="AF429" t="inlineStr"/>
       <c r="AG429" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303714/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303714/manifest</t>
         </is>
       </c>
       <c r="AH429" t="inlineStr"/>
@@ -50595,7 +50595,7 @@
       <c r="AF430" t="inlineStr"/>
       <c r="AG430" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303715/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303715/manifest</t>
         </is>
       </c>
       <c r="AH430" t="inlineStr"/>
@@ -50729,7 +50729,7 @@
       <c r="AF431" t="inlineStr"/>
       <c r="AG431" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303716/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303716/manifest</t>
         </is>
       </c>
       <c r="AH431" t="inlineStr"/>
@@ -50859,7 +50859,7 @@
       <c r="AF432" t="inlineStr"/>
       <c r="AG432" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303717/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303717/manifest</t>
         </is>
       </c>
       <c r="AH432" t="inlineStr"/>
@@ -50993,7 +50993,7 @@
       <c r="AF433" t="inlineStr"/>
       <c r="AG433" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303718/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303718/manifest</t>
         </is>
       </c>
       <c r="AH433" t="inlineStr"/>
@@ -51127,7 +51127,7 @@
       <c r="AF434" t="inlineStr"/>
       <c r="AG434" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303719/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303719/manifest</t>
         </is>
       </c>
       <c r="AH434" t="inlineStr"/>
@@ -51261,7 +51261,7 @@
       <c r="AF435" t="inlineStr"/>
       <c r="AG435" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303720/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303720/manifest</t>
         </is>
       </c>
       <c r="AH435" t="inlineStr"/>
@@ -51395,7 +51395,7 @@
       <c r="AF436" t="inlineStr"/>
       <c r="AG436" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303721/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303721/manifest</t>
         </is>
       </c>
       <c r="AH436" t="inlineStr"/>
@@ -51529,7 +51529,7 @@
       <c r="AF437" t="inlineStr"/>
       <c r="AG437" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303722/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303722/manifest</t>
         </is>
       </c>
       <c r="AH437" t="inlineStr"/>
@@ -51663,7 +51663,7 @@
       <c r="AF438" t="inlineStr"/>
       <c r="AG438" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303723/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303723/manifest</t>
         </is>
       </c>
       <c r="AH438" t="inlineStr"/>
@@ -51797,7 +51797,7 @@
       <c r="AF439" t="inlineStr"/>
       <c r="AG439" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303724/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303724/manifest</t>
         </is>
       </c>
       <c r="AH439" t="inlineStr"/>
@@ -51931,7 +51931,7 @@
       <c r="AF440" t="inlineStr"/>
       <c r="AG440" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303725/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303725/manifest</t>
         </is>
       </c>
       <c r="AH440" t="inlineStr"/>
@@ -52065,7 +52065,7 @@
       <c r="AF441" t="inlineStr"/>
       <c r="AG441" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303726/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303726/manifest</t>
         </is>
       </c>
       <c r="AH441" t="inlineStr"/>
@@ -52195,7 +52195,7 @@
       <c r="AF442" t="inlineStr"/>
       <c r="AG442" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303727/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303727/manifest</t>
         </is>
       </c>
       <c r="AH442" t="inlineStr"/>
@@ -52329,7 +52329,7 @@
       <c r="AF443" t="inlineStr"/>
       <c r="AG443" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303728/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303728/manifest</t>
         </is>
       </c>
       <c r="AH443" t="inlineStr"/>
@@ -52459,7 +52459,7 @@
       <c r="AF444" t="inlineStr"/>
       <c r="AG444" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303729/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303729/manifest</t>
         </is>
       </c>
       <c r="AH444" t="inlineStr"/>
@@ -52593,7 +52593,7 @@
       <c r="AF445" t="inlineStr"/>
       <c r="AG445" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303730/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303730/manifest</t>
         </is>
       </c>
       <c r="AH445" t="inlineStr"/>
@@ -52727,7 +52727,7 @@
       <c r="AF446" t="inlineStr"/>
       <c r="AG446" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303731/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303731/manifest</t>
         </is>
       </c>
       <c r="AH446" t="inlineStr"/>
@@ -52861,7 +52861,7 @@
       <c r="AF447" t="inlineStr"/>
       <c r="AG447" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303732/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303732/manifest</t>
         </is>
       </c>
       <c r="AH447" t="inlineStr"/>
@@ -52995,7 +52995,7 @@
       <c r="AF448" t="inlineStr"/>
       <c r="AG448" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303733/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303733/manifest</t>
         </is>
       </c>
       <c r="AH448" t="inlineStr"/>
@@ -53125,7 +53125,7 @@
       <c r="AF449" t="inlineStr"/>
       <c r="AG449" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303734/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303734/manifest</t>
         </is>
       </c>
       <c r="AH449" t="inlineStr"/>
@@ -53259,7 +53259,7 @@
       <c r="AF450" t="inlineStr"/>
       <c r="AG450" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303735/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303735/manifest</t>
         </is>
       </c>
       <c r="AH450" t="inlineStr"/>
@@ -53393,7 +53393,7 @@
       <c r="AF451" t="inlineStr"/>
       <c r="AG451" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303736/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303736/manifest</t>
         </is>
       </c>
       <c r="AH451" t="inlineStr"/>
@@ -53527,7 +53527,7 @@
       <c r="AF452" t="inlineStr"/>
       <c r="AG452" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303737/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303737/manifest</t>
         </is>
       </c>
       <c r="AH452" t="inlineStr"/>
@@ -53661,7 +53661,7 @@
       <c r="AF453" t="inlineStr"/>
       <c r="AG453" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303738/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303738/manifest</t>
         </is>
       </c>
       <c r="AH453" t="inlineStr"/>
@@ -53795,7 +53795,7 @@
       <c r="AF454" t="inlineStr"/>
       <c r="AG454" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303739/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303739/manifest</t>
         </is>
       </c>
       <c r="AH454" t="inlineStr"/>
@@ -53929,7 +53929,7 @@
       <c r="AF455" t="inlineStr"/>
       <c r="AG455" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303740/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303740/manifest</t>
         </is>
       </c>
       <c r="AH455" t="inlineStr"/>
@@ -54063,7 +54063,7 @@
       <c r="AF456" t="inlineStr"/>
       <c r="AG456" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303741/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303741/manifest</t>
         </is>
       </c>
       <c r="AH456" t="inlineStr"/>
@@ -54197,7 +54197,7 @@
       <c r="AF457" t="inlineStr"/>
       <c r="AG457" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303742/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303742/manifest</t>
         </is>
       </c>
       <c r="AH457" t="inlineStr"/>
@@ -54331,7 +54331,7 @@
       <c r="AF458" t="inlineStr"/>
       <c r="AG458" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303743/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303743/manifest</t>
         </is>
       </c>
       <c r="AH458" t="inlineStr"/>
@@ -54465,7 +54465,7 @@
       <c r="AF459" t="inlineStr"/>
       <c r="AG459" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303744/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303744/manifest</t>
         </is>
       </c>
       <c r="AH459" t="inlineStr"/>
@@ -54599,7 +54599,7 @@
       <c r="AF460" t="inlineStr"/>
       <c r="AG460" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303745/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303745/manifest</t>
         </is>
       </c>
       <c r="AH460" t="inlineStr"/>
@@ -54729,7 +54729,7 @@
       <c r="AF461" t="inlineStr"/>
       <c r="AG461" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303746/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303746/manifest</t>
         </is>
       </c>
       <c r="AH461" t="inlineStr"/>
@@ -54863,7 +54863,7 @@
       <c r="AF462" t="inlineStr"/>
       <c r="AG462" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303747/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303747/manifest</t>
         </is>
       </c>
       <c r="AH462" t="inlineStr"/>
@@ -54997,7 +54997,7 @@
       <c r="AF463" t="inlineStr"/>
       <c r="AG463" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303748/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303748/manifest</t>
         </is>
       </c>
       <c r="AH463" t="inlineStr"/>
@@ -55131,7 +55131,7 @@
       <c r="AF464" t="inlineStr"/>
       <c r="AG464" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303749/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303749/manifest</t>
         </is>
       </c>
       <c r="AH464" t="inlineStr"/>
@@ -55265,7 +55265,7 @@
       <c r="AF465" t="inlineStr"/>
       <c r="AG465" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303750/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303750/manifest</t>
         </is>
       </c>
       <c r="AH465" t="inlineStr"/>
@@ -55399,7 +55399,7 @@
       <c r="AF466" t="inlineStr"/>
       <c r="AG466" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303751/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303751/manifest</t>
         </is>
       </c>
       <c r="AH466" t="inlineStr"/>
@@ -55533,7 +55533,7 @@
       <c r="AF467" t="inlineStr"/>
       <c r="AG467" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303752/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303752/manifest</t>
         </is>
       </c>
       <c r="AH467" t="inlineStr"/>
@@ -55667,7 +55667,7 @@
       <c r="AF468" t="inlineStr"/>
       <c r="AG468" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303753/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303753/manifest</t>
         </is>
       </c>
       <c r="AH468" t="inlineStr"/>
@@ -55801,7 +55801,7 @@
       <c r="AF469" t="inlineStr"/>
       <c r="AG469" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303754/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303754/manifest</t>
         </is>
       </c>
       <c r="AH469" t="inlineStr"/>
@@ -55935,7 +55935,7 @@
       <c r="AF470" t="inlineStr"/>
       <c r="AG470" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303755/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303755/manifest</t>
         </is>
       </c>
       <c r="AH470" t="inlineStr"/>
@@ -56069,7 +56069,7 @@
       <c r="AF471" t="inlineStr"/>
       <c r="AG471" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303756/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303756/manifest</t>
         </is>
       </c>
       <c r="AH471" t="inlineStr"/>
@@ -56203,7 +56203,7 @@
       <c r="AF472" t="inlineStr"/>
       <c r="AG472" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303757/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303757/manifest</t>
         </is>
       </c>
       <c r="AH472" t="inlineStr"/>
@@ -56337,7 +56337,7 @@
       <c r="AF473" t="inlineStr"/>
       <c r="AG473" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303758/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303758/manifest</t>
         </is>
       </c>
       <c r="AH473" t="inlineStr"/>
@@ -56471,7 +56471,7 @@
       <c r="AF474" t="inlineStr"/>
       <c r="AG474" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303759/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303759/manifest</t>
         </is>
       </c>
       <c r="AH474" t="inlineStr"/>
@@ -56605,7 +56605,7 @@
       <c r="AF475" t="inlineStr"/>
       <c r="AG475" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303760/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303760/manifest</t>
         </is>
       </c>
       <c r="AH475" t="inlineStr"/>
@@ -56739,7 +56739,7 @@
       <c r="AF476" t="inlineStr"/>
       <c r="AG476" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303761/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303761/manifest</t>
         </is>
       </c>
       <c r="AH476" t="inlineStr"/>
@@ -56869,7 +56869,7 @@
       <c r="AF477" t="inlineStr"/>
       <c r="AG477" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303762/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303762/manifest</t>
         </is>
       </c>
       <c r="AH477" t="inlineStr"/>
@@ -57003,7 +57003,7 @@
       <c r="AF478" t="inlineStr"/>
       <c r="AG478" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303763/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303763/manifest</t>
         </is>
       </c>
       <c r="AH478" t="inlineStr"/>
@@ -57137,7 +57137,7 @@
       <c r="AF479" t="inlineStr"/>
       <c r="AG479" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303764/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303764/manifest</t>
         </is>
       </c>
       <c r="AH479" t="inlineStr"/>
@@ -57267,7 +57267,7 @@
       <c r="AF480" t="inlineStr"/>
       <c r="AG480" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303765/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303765/manifest</t>
         </is>
       </c>
       <c r="AH480" t="inlineStr"/>
@@ -57401,7 +57401,7 @@
       <c r="AF481" t="inlineStr"/>
       <c r="AG481" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303766/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303766/manifest</t>
         </is>
       </c>
       <c r="AH481" t="inlineStr"/>
@@ -57535,7 +57535,7 @@
       <c r="AF482" t="inlineStr"/>
       <c r="AG482" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303767/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303767/manifest</t>
         </is>
       </c>
       <c r="AH482" t="inlineStr"/>
@@ -57669,7 +57669,7 @@
       <c r="AF483" t="inlineStr"/>
       <c r="AG483" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303768/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303768/manifest</t>
         </is>
       </c>
       <c r="AH483" t="inlineStr"/>
@@ -57803,7 +57803,7 @@
       <c r="AF484" t="inlineStr"/>
       <c r="AG484" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303769/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303769/manifest</t>
         </is>
       </c>
       <c r="AH484" t="inlineStr"/>
@@ -57937,7 +57937,7 @@
       <c r="AF485" t="inlineStr"/>
       <c r="AG485" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303770/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303770/manifest</t>
         </is>
       </c>
       <c r="AH485" t="inlineStr"/>
@@ -58071,7 +58071,7 @@
       <c r="AF486" t="inlineStr"/>
       <c r="AG486" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303771/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303771/manifest</t>
         </is>
       </c>
       <c r="AH486" t="inlineStr"/>
@@ -58205,7 +58205,7 @@
       <c r="AF487" t="inlineStr"/>
       <c r="AG487" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303772/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303772/manifest</t>
         </is>
       </c>
       <c r="AH487" t="inlineStr"/>
@@ -58339,7 +58339,7 @@
       <c r="AF488" t="inlineStr"/>
       <c r="AG488" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303773/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303773/manifest</t>
         </is>
       </c>
       <c r="AH488" t="inlineStr"/>
@@ -58473,7 +58473,7 @@
       <c r="AF489" t="inlineStr"/>
       <c r="AG489" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303774/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303774/manifest</t>
         </is>
       </c>
       <c r="AH489" t="inlineStr"/>
@@ -58607,7 +58607,7 @@
       <c r="AF490" t="inlineStr"/>
       <c r="AG490" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303775/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303775/manifest</t>
         </is>
       </c>
       <c r="AH490" t="inlineStr"/>
@@ -58741,7 +58741,7 @@
       <c r="AF491" t="inlineStr"/>
       <c r="AG491" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303776/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303776/manifest</t>
         </is>
       </c>
       <c r="AH491" t="inlineStr"/>
@@ -58875,7 +58875,7 @@
       <c r="AF492" t="inlineStr"/>
       <c r="AG492" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303777/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303777/manifest</t>
         </is>
       </c>
       <c r="AH492" t="inlineStr"/>
@@ -59009,7 +59009,7 @@
       <c r="AF493" t="inlineStr"/>
       <c r="AG493" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303778/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303778/manifest</t>
         </is>
       </c>
       <c r="AH493" t="inlineStr"/>
@@ -59143,7 +59143,7 @@
       <c r="AF494" t="inlineStr"/>
       <c r="AG494" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303779/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303779/manifest</t>
         </is>
       </c>
       <c r="AH494" t="inlineStr"/>
@@ -59273,7 +59273,7 @@
       <c r="AF495" t="inlineStr"/>
       <c r="AG495" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303780/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303780/manifest</t>
         </is>
       </c>
       <c r="AH495" t="inlineStr"/>
@@ -59407,7 +59407,7 @@
       <c r="AF496" t="inlineStr"/>
       <c r="AG496" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303781/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303781/manifest</t>
         </is>
       </c>
       <c r="AH496" t="inlineStr"/>
@@ -59541,7 +59541,7 @@
       <c r="AF497" t="inlineStr"/>
       <c r="AG497" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303782/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303782/manifest</t>
         </is>
       </c>
       <c r="AH497" t="inlineStr"/>
@@ -59675,7 +59675,7 @@
       <c r="AF498" t="inlineStr"/>
       <c r="AG498" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303783/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303783/manifest</t>
         </is>
       </c>
       <c r="AH498" t="inlineStr"/>
@@ -59809,7 +59809,7 @@
       <c r="AF499" t="inlineStr"/>
       <c r="AG499" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303784/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303784/manifest</t>
         </is>
       </c>
       <c r="AH499" t="inlineStr"/>
@@ -59943,7 +59943,7 @@
       <c r="AF500" t="inlineStr"/>
       <c r="AG500" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303785/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303785/manifest</t>
         </is>
       </c>
       <c r="AH500" t="inlineStr"/>
@@ -60077,7 +60077,7 @@
       <c r="AF501" t="inlineStr"/>
       <c r="AG501" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303786/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303786/manifest</t>
         </is>
       </c>
       <c r="AH501" t="inlineStr"/>
@@ -60211,7 +60211,7 @@
       <c r="AF502" t="inlineStr"/>
       <c r="AG502" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303787/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303787/manifest</t>
         </is>
       </c>
       <c r="AH502" t="inlineStr"/>
@@ -60345,7 +60345,7 @@
       <c r="AF503" t="inlineStr"/>
       <c r="AG503" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303788/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303788/manifest</t>
         </is>
       </c>
       <c r="AH503" t="inlineStr"/>
@@ -60479,7 +60479,7 @@
       <c r="AF504" t="inlineStr"/>
       <c r="AG504" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303789/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303789/manifest</t>
         </is>
       </c>
       <c r="AH504" t="inlineStr"/>
@@ -60613,7 +60613,7 @@
       <c r="AF505" t="inlineStr"/>
       <c r="AG505" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303790/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303790/manifest</t>
         </is>
       </c>
       <c r="AH505" t="inlineStr"/>
@@ -60743,7 +60743,7 @@
       <c r="AF506" t="inlineStr"/>
       <c r="AG506" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303791/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303791/manifest</t>
         </is>
       </c>
       <c r="AH506" t="inlineStr"/>
@@ -60877,7 +60877,7 @@
       <c r="AF507" t="inlineStr"/>
       <c r="AG507" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303792/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303792/manifest</t>
         </is>
       </c>
       <c r="AH507" t="inlineStr"/>
@@ -61011,7 +61011,7 @@
       <c r="AF508" t="inlineStr"/>
       <c r="AG508" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303793/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303793/manifest</t>
         </is>
       </c>
       <c r="AH508" t="inlineStr"/>
@@ -61141,7 +61141,7 @@
       <c r="AF509" t="inlineStr"/>
       <c r="AG509" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303794/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303794/manifest</t>
         </is>
       </c>
       <c r="AH509" t="inlineStr"/>
@@ -61275,7 +61275,7 @@
       <c r="AF510" t="inlineStr"/>
       <c r="AG510" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303795/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303795/manifest</t>
         </is>
       </c>
       <c r="AH510" t="inlineStr"/>
@@ -61409,7 +61409,7 @@
       <c r="AF511" t="inlineStr"/>
       <c r="AG511" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303796/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303796/manifest</t>
         </is>
       </c>
       <c r="AH511" t="inlineStr"/>
@@ -61543,7 +61543,7 @@
       <c r="AF512" t="inlineStr"/>
       <c r="AG512" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303797/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303797/manifest</t>
         </is>
       </c>
       <c r="AH512" t="inlineStr"/>
@@ -61677,7 +61677,7 @@
       <c r="AF513" t="inlineStr"/>
       <c r="AG513" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303798/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303798/manifest</t>
         </is>
       </c>
       <c r="AH513" t="inlineStr"/>
@@ -61811,7 +61811,7 @@
       <c r="AF514" t="inlineStr"/>
       <c r="AG514" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303799/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303799/manifest</t>
         </is>
       </c>
       <c r="AH514" t="inlineStr"/>
@@ -61945,7 +61945,7 @@
       <c r="AF515" t="inlineStr"/>
       <c r="AG515" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303800/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303800/manifest</t>
         </is>
       </c>
       <c r="AH515" t="inlineStr"/>
@@ -62079,7 +62079,7 @@
       <c r="AF516" t="inlineStr"/>
       <c r="AG516" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303801/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303801/manifest</t>
         </is>
       </c>
       <c r="AH516" t="inlineStr"/>
@@ -62213,7 +62213,7 @@
       <c r="AF517" t="inlineStr"/>
       <c r="AG517" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303802/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303802/manifest</t>
         </is>
       </c>
       <c r="AH517" t="inlineStr"/>
@@ -62347,7 +62347,7 @@
       <c r="AF518" t="inlineStr"/>
       <c r="AG518" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303803/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303803/manifest</t>
         </is>
       </c>
       <c r="AH518" t="inlineStr"/>
@@ -62481,7 +62481,7 @@
       <c r="AF519" t="inlineStr"/>
       <c r="AG519" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303804/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303804/manifest</t>
         </is>
       </c>
       <c r="AH519" t="inlineStr"/>
@@ -62615,7 +62615,7 @@
       <c r="AF520" t="inlineStr"/>
       <c r="AG520" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303805/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303805/manifest</t>
         </is>
       </c>
       <c r="AH520" t="inlineStr"/>
@@ -62749,7 +62749,7 @@
       <c r="AF521" t="inlineStr"/>
       <c r="AG521" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303806/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303806/manifest</t>
         </is>
       </c>
       <c r="AH521" t="inlineStr"/>
@@ -62883,7 +62883,7 @@
       <c r="AF522" t="inlineStr"/>
       <c r="AG522" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303807/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303807/manifest</t>
         </is>
       </c>
       <c r="AH522" t="inlineStr"/>
@@ -63013,7 +63013,7 @@
       <c r="AF523" t="inlineStr"/>
       <c r="AG523" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303808/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303808/manifest</t>
         </is>
       </c>
       <c r="AH523" t="inlineStr"/>
@@ -63147,7 +63147,7 @@
       <c r="AF524" t="inlineStr"/>
       <c r="AG524" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303809/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303809/manifest</t>
         </is>
       </c>
       <c r="AH524" t="inlineStr"/>
@@ -63281,7 +63281,7 @@
       <c r="AF525" t="inlineStr"/>
       <c r="AG525" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303810/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303810/manifest</t>
         </is>
       </c>
       <c r="AH525" t="inlineStr"/>
@@ -63415,7 +63415,7 @@
       <c r="AF526" t="inlineStr"/>
       <c r="AG526" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303811/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303811/manifest</t>
         </is>
       </c>
       <c r="AH526" t="inlineStr"/>
@@ -63549,7 +63549,7 @@
       <c r="AF527" t="inlineStr"/>
       <c r="AG527" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303812/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303812/manifest</t>
         </is>
       </c>
       <c r="AH527" t="inlineStr"/>
@@ -63683,7 +63683,7 @@
       <c r="AF528" t="inlineStr"/>
       <c r="AG528" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303813/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303813/manifest</t>
         </is>
       </c>
       <c r="AH528" t="inlineStr"/>
@@ -63817,7 +63817,7 @@
       <c r="AF529" t="inlineStr"/>
       <c r="AG529" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303814/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303814/manifest</t>
         </is>
       </c>
       <c r="AH529" t="inlineStr"/>
@@ -63951,7 +63951,7 @@
       <c r="AF530" t="inlineStr"/>
       <c r="AG530" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303815/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303815/manifest</t>
         </is>
       </c>
       <c r="AH530" t="inlineStr"/>
@@ -64085,7 +64085,7 @@
       <c r="AF531" t="inlineStr"/>
       <c r="AG531" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303816/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303816/manifest</t>
         </is>
       </c>
       <c r="AH531" t="inlineStr"/>
@@ -64219,7 +64219,7 @@
       <c r="AF532" t="inlineStr"/>
       <c r="AG532" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303817/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303817/manifest</t>
         </is>
       </c>
       <c r="AH532" t="inlineStr"/>
@@ -64353,7 +64353,7 @@
       <c r="AF533" t="inlineStr"/>
       <c r="AG533" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303818/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303818/manifest</t>
         </is>
       </c>
       <c r="AH533" t="inlineStr"/>
@@ -64487,7 +64487,7 @@
       <c r="AF534" t="inlineStr"/>
       <c r="AG534" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303819/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303819/manifest</t>
         </is>
       </c>
       <c r="AH534" t="inlineStr"/>
@@ -64617,7 +64617,7 @@
       <c r="AF535" t="inlineStr"/>
       <c r="AG535" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303820/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303820/manifest</t>
         </is>
       </c>
       <c r="AH535" t="inlineStr"/>
@@ -64751,7 +64751,7 @@
       <c r="AF536" t="inlineStr"/>
       <c r="AG536" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303821/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303821/manifest</t>
         </is>
       </c>
       <c r="AH536" t="inlineStr"/>
@@ -64885,7 +64885,7 @@
       <c r="AF537" t="inlineStr"/>
       <c r="AG537" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303822/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303822/manifest</t>
         </is>
       </c>
       <c r="AH537" t="inlineStr"/>
@@ -65019,7 +65019,7 @@
       <c r="AF538" t="inlineStr"/>
       <c r="AG538" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303823/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303823/manifest</t>
         </is>
       </c>
       <c r="AH538" t="inlineStr"/>
@@ -65153,7 +65153,7 @@
       <c r="AF539" t="inlineStr"/>
       <c r="AG539" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303824/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303824/manifest</t>
         </is>
       </c>
       <c r="AH539" t="inlineStr"/>
@@ -65287,7 +65287,7 @@
       <c r="AF540" t="inlineStr"/>
       <c r="AG540" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303825/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303825/manifest</t>
         </is>
       </c>
       <c r="AH540" t="inlineStr"/>
@@ -65417,7 +65417,7 @@
       <c r="AF541" t="inlineStr"/>
       <c r="AG541" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303826/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303826/manifest</t>
         </is>
       </c>
       <c r="AH541" t="inlineStr"/>
@@ -65551,7 +65551,7 @@
       <c r="AF542" t="inlineStr"/>
       <c r="AG542" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303827/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303827/manifest</t>
         </is>
       </c>
       <c r="AH542" t="inlineStr"/>
@@ -65685,7 +65685,7 @@
       <c r="AF543" t="inlineStr"/>
       <c r="AG543" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303828/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303828/manifest</t>
         </is>
       </c>
       <c r="AH543" t="inlineStr"/>
@@ -65819,7 +65819,7 @@
       <c r="AF544" t="inlineStr"/>
       <c r="AG544" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303829/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303829/manifest</t>
         </is>
       </c>
       <c r="AH544" t="inlineStr"/>
@@ -65949,7 +65949,7 @@
       <c r="AF545" t="inlineStr"/>
       <c r="AG545" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303830/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303830/manifest</t>
         </is>
       </c>
       <c r="AH545" t="inlineStr"/>
@@ -66083,7 +66083,7 @@
       <c r="AF546" t="inlineStr"/>
       <c r="AG546" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303831/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303831/manifest</t>
         </is>
       </c>
       <c r="AH546" t="inlineStr"/>
@@ -66217,7 +66217,7 @@
       <c r="AF547" t="inlineStr"/>
       <c r="AG547" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303832/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303832/manifest</t>
         </is>
       </c>
       <c r="AH547" t="inlineStr"/>
@@ -66351,7 +66351,7 @@
       <c r="AF548" t="inlineStr"/>
       <c r="AG548" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303833/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303833/manifest</t>
         </is>
       </c>
       <c r="AH548" t="inlineStr"/>
@@ -66485,7 +66485,7 @@
       <c r="AF549" t="inlineStr"/>
       <c r="AG549" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303834/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303834/manifest</t>
         </is>
       </c>
       <c r="AH549" t="inlineStr"/>
@@ -66615,7 +66615,7 @@
       <c r="AF550" t="inlineStr"/>
       <c r="AG550" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303835/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303835/manifest</t>
         </is>
       </c>
       <c r="AH550" t="inlineStr"/>
@@ -66745,7 +66745,7 @@
       <c r="AF551" t="inlineStr"/>
       <c r="AG551" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303836/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303836/manifest</t>
         </is>
       </c>
       <c r="AH551" t="inlineStr"/>
@@ -66879,7 +66879,7 @@
       <c r="AF552" t="inlineStr"/>
       <c r="AG552" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303837/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303837/manifest</t>
         </is>
       </c>
       <c r="AH552" t="inlineStr"/>
@@ -67013,7 +67013,7 @@
       <c r="AF553" t="inlineStr"/>
       <c r="AG553" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303838/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303838/manifest</t>
         </is>
       </c>
       <c r="AH553" t="inlineStr"/>
@@ -67147,7 +67147,7 @@
       <c r="AF554" t="inlineStr"/>
       <c r="AG554" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303839/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303839/manifest</t>
         </is>
       </c>
       <c r="AH554" t="inlineStr"/>
@@ -67281,7 +67281,7 @@
       <c r="AF555" t="inlineStr"/>
       <c r="AG555" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303840/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303840/manifest</t>
         </is>
       </c>
       <c r="AH555" t="inlineStr"/>
@@ -67415,7 +67415,7 @@
       <c r="AF556" t="inlineStr"/>
       <c r="AG556" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303841/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303841/manifest</t>
         </is>
       </c>
       <c r="AH556" t="inlineStr"/>
@@ -67549,7 +67549,7 @@
       <c r="AF557" t="inlineStr"/>
       <c r="AG557" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303842/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303842/manifest</t>
         </is>
       </c>
       <c r="AH557" t="inlineStr"/>
@@ -67683,7 +67683,7 @@
       <c r="AF558" t="inlineStr"/>
       <c r="AG558" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303843/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303843/manifest</t>
         </is>
       </c>
       <c r="AH558" t="inlineStr"/>
@@ -67817,7 +67817,7 @@
       <c r="AF559" t="inlineStr"/>
       <c r="AG559" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303844/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303844/manifest</t>
         </is>
       </c>
       <c r="AH559" t="inlineStr"/>
@@ -67951,7 +67951,7 @@
       <c r="AF560" t="inlineStr"/>
       <c r="AG560" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303845/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303845/manifest</t>
         </is>
       </c>
       <c r="AH560" t="inlineStr"/>
@@ -68085,7 +68085,7 @@
       <c r="AF561" t="inlineStr"/>
       <c r="AG561" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303846/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303846/manifest</t>
         </is>
       </c>
       <c r="AH561" t="inlineStr"/>
@@ -68219,7 +68219,7 @@
       <c r="AF562" t="inlineStr"/>
       <c r="AG562" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303847/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303847/manifest</t>
         </is>
       </c>
       <c r="AH562" t="inlineStr"/>
@@ -68353,7 +68353,7 @@
       <c r="AF563" t="inlineStr"/>
       <c r="AG563" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303848/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303848/manifest</t>
         </is>
       </c>
       <c r="AH563" t="inlineStr"/>
@@ -68487,7 +68487,7 @@
       <c r="AF564" t="inlineStr"/>
       <c r="AG564" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303849/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303849/manifest</t>
         </is>
       </c>
       <c r="AH564" t="inlineStr"/>
@@ -68621,7 +68621,7 @@
       <c r="AF565" t="inlineStr"/>
       <c r="AG565" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303850/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303850/manifest</t>
         </is>
       </c>
       <c r="AH565" t="inlineStr"/>
@@ -68755,7 +68755,7 @@
       <c r="AF566" t="inlineStr"/>
       <c r="AG566" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303851/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303851/manifest</t>
         </is>
       </c>
       <c r="AH566" t="inlineStr"/>
@@ -68885,7 +68885,7 @@
       <c r="AF567" t="inlineStr"/>
       <c r="AG567" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303852/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303852/manifest</t>
         </is>
       </c>
       <c r="AH567" t="inlineStr"/>
@@ -69019,7 +69019,7 @@
       <c r="AF568" t="inlineStr"/>
       <c r="AG568" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303853/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303853/manifest</t>
         </is>
       </c>
       <c r="AH568" t="inlineStr"/>
@@ -69153,7 +69153,7 @@
       <c r="AF569" t="inlineStr"/>
       <c r="AG569" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303854/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303854/manifest</t>
         </is>
       </c>
       <c r="AH569" t="inlineStr"/>
@@ -69287,7 +69287,7 @@
       <c r="AF570" t="inlineStr"/>
       <c r="AG570" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303855/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303855/manifest</t>
         </is>
       </c>
       <c r="AH570" t="inlineStr"/>
@@ -69421,7 +69421,7 @@
       <c r="AF571" t="inlineStr"/>
       <c r="AG571" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303856/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303856/manifest</t>
         </is>
       </c>
       <c r="AH571" t="inlineStr"/>
@@ -69555,7 +69555,7 @@
       <c r="AF572" t="inlineStr"/>
       <c r="AG572" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303857/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303857/manifest</t>
         </is>
       </c>
       <c r="AH572" t="inlineStr"/>
@@ -69689,7 +69689,7 @@
       <c r="AF573" t="inlineStr"/>
       <c r="AG573" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303858/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303858/manifest</t>
         </is>
       </c>
       <c r="AH573" t="inlineStr"/>
@@ -69819,7 +69819,7 @@
       <c r="AF574" t="inlineStr"/>
       <c r="AG574" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303859/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303859/manifest</t>
         </is>
       </c>
       <c r="AH574" t="inlineStr"/>
@@ -69953,7 +69953,7 @@
       <c r="AF575" t="inlineStr"/>
       <c r="AG575" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303860/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303860/manifest</t>
         </is>
       </c>
       <c r="AH575" t="inlineStr"/>
@@ -70087,7 +70087,7 @@
       <c r="AF576" t="inlineStr"/>
       <c r="AG576" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303861/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303861/manifest</t>
         </is>
       </c>
       <c r="AH576" t="inlineStr"/>
@@ -70221,7 +70221,7 @@
       <c r="AF577" t="inlineStr"/>
       <c r="AG577" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303862/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303862/manifest</t>
         </is>
       </c>
       <c r="AH577" t="inlineStr"/>
@@ -70355,7 +70355,7 @@
       <c r="AF578" t="inlineStr"/>
       <c r="AG578" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303863/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303863/manifest</t>
         </is>
       </c>
       <c r="AH578" t="inlineStr"/>
@@ -70489,7 +70489,7 @@
       <c r="AF579" t="inlineStr"/>
       <c r="AG579" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303864/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303864/manifest</t>
         </is>
       </c>
       <c r="AH579" t="inlineStr"/>
@@ -70623,7 +70623,7 @@
       <c r="AF580" t="inlineStr"/>
       <c r="AG580" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303865/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303865/manifest</t>
         </is>
       </c>
       <c r="AH580" t="inlineStr"/>
@@ -70757,7 +70757,7 @@
       <c r="AF581" t="inlineStr"/>
       <c r="AG581" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303866/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303866/manifest</t>
         </is>
       </c>
       <c r="AH581" t="inlineStr"/>
@@ -70891,7 +70891,7 @@
       <c r="AF582" t="inlineStr"/>
       <c r="AG582" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303867/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303867/manifest</t>
         </is>
       </c>
       <c r="AH582" t="inlineStr"/>
@@ -71025,7 +71025,7 @@
       <c r="AF583" t="inlineStr"/>
       <c r="AG583" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303868/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303868/manifest</t>
         </is>
       </c>
       <c r="AH583" t="inlineStr"/>
@@ -71159,7 +71159,7 @@
       <c r="AF584" t="inlineStr"/>
       <c r="AG584" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303869/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303869/manifest</t>
         </is>
       </c>
       <c r="AH584" t="inlineStr"/>
@@ -71293,7 +71293,7 @@
       <c r="AF585" t="inlineStr"/>
       <c r="AG585" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303870/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303870/manifest</t>
         </is>
       </c>
       <c r="AH585" t="inlineStr"/>
@@ -71427,7 +71427,7 @@
       <c r="AF586" t="inlineStr"/>
       <c r="AG586" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303871/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303871/manifest</t>
         </is>
       </c>
       <c r="AH586" t="inlineStr"/>
@@ -71561,7 +71561,7 @@
       <c r="AF587" t="inlineStr"/>
       <c r="AG587" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303872/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303872/manifest</t>
         </is>
       </c>
       <c r="AH587" t="inlineStr"/>
@@ -71695,7 +71695,7 @@
       <c r="AF588" t="inlineStr"/>
       <c r="AG588" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303873/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303873/manifest</t>
         </is>
       </c>
       <c r="AH588" t="inlineStr"/>
@@ -71829,7 +71829,7 @@
       <c r="AF589" t="inlineStr"/>
       <c r="AG589" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303874/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303874/manifest</t>
         </is>
       </c>
       <c r="AH589" t="inlineStr"/>
@@ -71963,7 +71963,7 @@
       <c r="AF590" t="inlineStr"/>
       <c r="AG590" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303875/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303875/manifest</t>
         </is>
       </c>
       <c r="AH590" t="inlineStr"/>
@@ -72097,7 +72097,7 @@
       <c r="AF591" t="inlineStr"/>
       <c r="AG591" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303876/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303876/manifest</t>
         </is>
       </c>
       <c r="AH591" t="inlineStr"/>
@@ -72231,7 +72231,7 @@
       <c r="AF592" t="inlineStr"/>
       <c r="AG592" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303877/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303877/manifest</t>
         </is>
       </c>
       <c r="AH592" t="inlineStr"/>
@@ -72365,7 +72365,7 @@
       <c r="AF593" t="inlineStr"/>
       <c r="AG593" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303878/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303878/manifest</t>
         </is>
       </c>
       <c r="AH593" t="inlineStr"/>
@@ -72499,7 +72499,7 @@
       <c r="AF594" t="inlineStr"/>
       <c r="AG594" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303879/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303879/manifest</t>
         </is>
       </c>
       <c r="AH594" t="inlineStr"/>
@@ -72633,7 +72633,7 @@
       <c r="AF595" t="inlineStr"/>
       <c r="AG595" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303880/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303880/manifest</t>
         </is>
       </c>
       <c r="AH595" t="inlineStr"/>
@@ -72767,7 +72767,7 @@
       <c r="AF596" t="inlineStr"/>
       <c r="AG596" t="inlineStr">
         <is>
-          <t>https://kotenseki.nijl.ac.jp/biblio/100303881/manifest</t>
+          <t>https://kokusho.nijl.ac.jp/biblio/100303881/manifest</t>
         </is>
       </c>
       <c r="AH596" t="inlineStr"/>
